--- a/Datas/BuffData.xlsx
+++ b/Datas/BuffData.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="44">
   <si>
     <t>id</t>
   </si>
@@ -81,9 +81,6 @@
     <t>lifeTime</t>
   </si>
   <si>
-    <t xml:space="preserve">coverBuffs </t>
-  </si>
-  <si>
     <t>buffactionType</t>
   </si>
   <si>
@@ -120,98 +117,118 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>冰冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,-1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>眩晕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>失明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,-50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中毒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,-40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,-30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>厄运</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷降低攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刺颈降低防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,5,9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流血</t>
+  </si>
+  <si>
+    <t>失明</t>
+  </si>
+  <si>
+    <t>中毒</t>
+  </si>
+  <si>
+    <t>降防御</t>
+  </si>
+  <si>
+    <t>降攻击</t>
+  </si>
+  <si>
     <t>probability</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>冰冻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,-1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>眩晕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>流血</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>失明</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,-50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中毒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,-40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,-30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AttributeType</t>
-  </si>
-  <si>
-    <t>厄运</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷降低攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刺颈降低防御</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,5,9</t>
+    <t>attributeType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coverBuffs</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -276,7 +293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -285,6 +302,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -572,7 +592,7 @@
   <cols>
     <col min="1" max="3" width="10.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.875" style="1"/>
-    <col min="5" max="5" width="9" style="1"/>
+    <col min="5" max="5" width="14.375" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.75" style="1" customWidth="1"/>
     <col min="7" max="9" width="15.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="10.75" style="1" customWidth="1"/>
@@ -582,40 +602,40 @@
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -629,31 +649,31 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -661,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
@@ -673,16 +693,19 @@
         <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -690,7 +713,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
@@ -702,16 +725,19 @@
         <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -719,7 +745,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1">
         <v>2</v>
@@ -731,16 +757,19 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -748,7 +777,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
@@ -760,16 +789,19 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -777,7 +809,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
@@ -789,16 +821,19 @@
         <v>5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -806,7 +841,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
@@ -818,16 +853,19 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
@@ -835,7 +873,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
@@ -853,10 +891,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -864,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1">
         <v>2</v>
@@ -882,10 +923,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -893,7 +937,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1">
         <v>2</v>
@@ -905,21 +949,25 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Datas/BuffData.xlsx
+++ b/Datas/BuffData.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
   <si>
     <t>id</t>
   </si>
@@ -229,6 +229,14 @@
   </si>
   <si>
     <t>coverBuffs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回血</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -587,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:L12"/>
+  <dimension ref="A2:L13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.75" style="1" customWidth="1"/>
@@ -964,6 +972,38 @@
         <v>32</v>
       </c>
     </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>100</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/BuffData.xlsx
+++ b/Datas/BuffData.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -237,6 +237,42 @@
   </si>
   <si>
     <t>回血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加幸运</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -595,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:L13"/>
+  <dimension ref="A2:L17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.75" style="1" customWidth="1"/>
@@ -998,10 +1034,138 @@
         <v>44</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1">
+        <v>100</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>11</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>100</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>12</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>100</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1">
+        <v>100</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>14</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/BuffData.xlsx
+++ b/Datas/BuffData.xlsx
@@ -1057,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
